--- a/test_files/file1.xlsx
+++ b/test_files/file1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -28,10 +28,10 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Dollar</t>
-  </si>
-  <si>
-    <t>Rupees</t>
+    <t>Lead</t>
+  </si>
+  <si>
+    <t>Notes</t>
   </si>
   <si>
     <t>20-04-2024</t>
@@ -50,6 +50,15 @@
   </si>
   <si>
     <t>ETH</t>
+  </si>
+  <si>
+    <t>Rakesh</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Initial</t>
   </si>
 </sst>
 </file>
@@ -407,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -443,68 +452,28 @@
       <c r="D2">
         <v>1.5</v>
       </c>
-      <c r="E2">
-        <v>1000</v>
-      </c>
-      <c r="F2">
-        <v>80000</v>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>1.5</v>
-      </c>
-      <c r="E3">
-        <v>1000</v>
-      </c>
-      <c r="F3">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4">
-        <v>2000</v>
-      </c>
-      <c r="F4">
-        <v>160000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2000</v>
-      </c>
-      <c r="F5">
-        <v>160000</v>
+      <c r="E3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
